--- a/backend/app/ASC_Users.xlsx
+++ b/backend/app/ASC_Users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aasti\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{069FDE98-B8F0-4FEA-BF11-FB4F27E6F180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1338B6-DF7A-45F9-995C-BE919A2EC7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3548" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3554" uniqueCount="864">
   <si>
     <t>Role</t>
   </si>
@@ -2609,6 +2609,12 @@
   </si>
   <si>
     <t>KRUSHNA CHANDRA GURU</t>
+  </si>
+  <si>
+    <t>Distributor</t>
+  </si>
+  <si>
+    <t>a</t>
   </si>
 </sst>
 </file>
@@ -3018,7 +3024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H591"/>
+  <dimension ref="A1:H592"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.81640625" style="3" bestFit="1" customWidth="1"/>
@@ -18398,6 +18404,29 @@
         <v>655</v>
       </c>
     </row>
+    <row r="592" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A592" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="B592" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="C592">
+        <v>5858360825</v>
+      </c>
+      <c r="E592" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="F592" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="G592" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="H592" s="3" t="s">
+        <v>655</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
